--- a/DateBase/orders/Dang Nguyen 195_2026-8-31.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-8-31.xlsx
@@ -1303,6 +1303,9 @@
       <c r="G2" t="str">
         <v>02524156445102051010101210301025101215101510108515155101086151110881598825121010522015165101555152105555555510101010101055151010555101030301510105105510</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
